--- a/doc/devNote/日记/日记表格.xlsx
+++ b/doc/devNote/日记/日记表格.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\idea_project\myStep\myStep\doc\devNote\日记\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFA7BFC-D857-4922-BEB7-BB864C7CF8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27428" windowHeight="13234"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>文章表</t>
   </si>
@@ -55,12 +49,12 @@
     <t>待办表</t>
   </si>
   <si>
+    <t>类型表</t>
+  </si>
+  <si>
     <t>统计视图</t>
   </si>
   <si>
-    <t>类型表</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -118,7 +112,7 @@
     <t>展示顺序</t>
   </si>
   <si>
-    <t>时间</t>
+    <t>写作时间</t>
   </si>
   <si>
     <t>评论人名称</t>
@@ -127,21 +121,27 @@
     <t>分类（1开发，2生活）</t>
   </si>
   <si>
+    <t>记忆中的时间</t>
+  </si>
+  <si>
     <t>评论人头像</t>
   </si>
   <si>
     <t>补充信息</t>
   </si>
   <si>
+    <t>天气id</t>
+  </si>
+  <si>
+    <t>父评论 ID（支持评论回复功能，0 表示一级评论）</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>心情</t>
   </si>
   <si>
-    <t>父评论 ID（支持评论回复功能，0 表示一级评论）</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
     <t>写作者名称</t>
   </si>
   <si>
@@ -149,6 +149,21 @@
   </si>
   <si>
     <t>写作者头像</t>
+  </si>
+  <si>
+    <t>图片地址逗号分割</t>
+  </si>
+  <si>
+    <t>是否星标</t>
+  </si>
+  <si>
+    <t>发生地址</t>
+  </si>
+  <si>
+    <t>文章表-标签关联表</t>
+  </si>
+  <si>
+    <t>文章id</t>
   </si>
   <si>
     <t>标签id</t>
@@ -157,8 +172,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,7 +191,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -179,21 +200,345 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -201,9 +546,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -218,24 +805,68 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -249,23 +880,17 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1025" name="AutoShape 1" descr="image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053E1EFB-BB29-A862-6FEE-8510216635F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="image"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
       </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="9386888" y="0"/>
-          <a:ext cx="304800" cy="304800"/>
+          <a:off x="10009505" y="0"/>
+          <a:ext cx="304800" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -531,19 +1156,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultColWidth="14.59765625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="14.5945945945946" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1"/>
+    <col min="1" max="1" width="25.2522522522523" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" ht="18" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -563,13 +1188,13 @@
         <v>5</v>
       </c>
       <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -592,7 +1217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -615,7 +1240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -638,7 +1263,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -655,7 +1280,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -669,79 +1294,111 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>